--- a/backend/data/financials_by_company/1218.TW.xlsx
+++ b/backend/data/financials_by_company/1218.TW.xlsx
@@ -662,576 +662,576 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-1059598.496693</v>
+        <v>32188.430171</v>
       </c>
       <c r="C2" t="n">
-        <v>0.157421</v>
+        <v>0.068632</v>
       </c>
       <c r="D2" t="n">
-        <v>1040437000</v>
+        <v>751295000</v>
       </c>
       <c r="E2" t="n">
-        <v>-6731000</v>
+        <v>469000</v>
       </c>
       <c r="F2" t="n">
-        <v>-6731000</v>
+        <v>469000</v>
       </c>
       <c r="G2" t="n">
-        <v>742411000</v>
+        <v>591827000</v>
       </c>
       <c r="H2" t="n">
-        <v>148763000</v>
+        <v>104769000</v>
       </c>
       <c r="I2" t="n">
-        <v>8792097000</v>
+        <v>8409291000</v>
       </c>
       <c r="J2" t="n">
-        <v>1033706000</v>
+        <v>751764000</v>
       </c>
       <c r="K2" t="n">
-        <v>884943000</v>
+        <v>646995000</v>
       </c>
       <c r="L2" t="n">
-        <v>42447000</v>
+        <v>-7004000</v>
       </c>
       <c r="M2" t="n">
-        <v>3553000</v>
+        <v>11359000</v>
       </c>
       <c r="N2" t="n">
-        <v>46000000</v>
+        <v>4355000</v>
       </c>
       <c r="O2" t="n">
-        <v>748082401.503307</v>
+        <v>591390188.430171</v>
       </c>
       <c r="P2" t="n">
-        <v>742411000</v>
+        <v>591827000</v>
       </c>
       <c r="Q2" t="n">
-        <v>10057186000</v>
+        <v>9735859000</v>
       </c>
       <c r="R2" t="n">
-        <v>487315000</v>
+        <v>488036000</v>
       </c>
       <c r="S2" t="n">
         <v>486393000</v>
       </c>
       <c r="T2" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="U2" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="V2" t="n">
-        <v>742411000</v>
+        <v>591827000</v>
       </c>
       <c r="W2" t="n">
-        <v>742411000</v>
+        <v>591827000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>742411000</v>
+        <v>591827000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-230000</v>
+        <v>-184000</v>
       </c>
       <c r="AA2" t="n">
-        <v>742641000</v>
+        <v>592011000</v>
       </c>
       <c r="AB2" t="n">
-        <v>742641000</v>
+        <v>592011000</v>
       </c>
       <c r="AC2" t="n">
-        <v>138749000</v>
+        <v>43625000</v>
       </c>
       <c r="AD2" t="n">
-        <v>881390000</v>
+        <v>635636000</v>
       </c>
       <c r="AE2" t="n">
-        <v>166423000</v>
+        <v>88950000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-6731000</v>
+        <v>469000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-278000</v>
+        <v>-702000</v>
       </c>
       <c r="AH2" t="n">
-        <v>7009000</v>
+        <v>233000</v>
       </c>
       <c r="AI2" t="n">
-        <v>42447000</v>
+        <v>-7004000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3553000</v>
+        <v>11359000</v>
       </c>
       <c r="AK2" t="n">
-        <v>46000000</v>
+        <v>4355000</v>
       </c>
       <c r="AL2" t="n">
-        <v>625259000</v>
+        <v>209119000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1265089000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>29981000</v>
-      </c>
+        <v>1326568000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-471000</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>1235108000</v>
+        <v>1326568000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>960878000</v>
+        <v>955655000</v>
       </c>
       <c r="AR2" t="n">
-        <v>274230000</v>
+        <v>370913000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1890348000</v>
+        <v>1535687000</v>
       </c>
       <c r="AT2" t="n">
-        <v>8792097000</v>
+        <v>8409291000</v>
       </c>
       <c r="AU2" t="n">
-        <v>10682445000</v>
+        <v>9944978000</v>
       </c>
       <c r="AV2" t="n">
-        <v>10682445000</v>
+        <v>9944978000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-60800</v>
+        <v>-316359.10387</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2</v>
+        <v>0.047105</v>
       </c>
       <c r="D3" t="n">
-        <v>288333000</v>
+        <v>6351666000</v>
       </c>
       <c r="E3" t="n">
-        <v>-304000</v>
+        <v>-6716000</v>
       </c>
       <c r="F3" t="n">
-        <v>-304000</v>
+        <v>-6716000</v>
       </c>
       <c r="G3" t="n">
-        <v>-80870000</v>
+        <v>5918495000</v>
       </c>
       <c r="H3" t="n">
-        <v>144160000</v>
+        <v>106788000</v>
       </c>
       <c r="I3" t="n">
-        <v>9678785000</v>
+        <v>9623679000</v>
       </c>
       <c r="J3" t="n">
-        <v>288029000</v>
+        <v>6344950000</v>
       </c>
       <c r="K3" t="n">
-        <v>143869000</v>
+        <v>6238162000</v>
       </c>
       <c r="L3" t="n">
-        <v>4629000</v>
+        <v>-19399000</v>
       </c>
       <c r="M3" t="n">
-        <v>20977000</v>
+        <v>27012000</v>
       </c>
       <c r="N3" t="n">
-        <v>25606000</v>
+        <v>7613000</v>
       </c>
       <c r="O3" t="n">
-        <v>-80626800</v>
+        <v>5924894640.89613</v>
       </c>
       <c r="P3" t="n">
-        <v>-80870000</v>
+        <v>5918495000</v>
       </c>
       <c r="Q3" t="n">
-        <v>11296178000</v>
+        <v>11454703000</v>
       </c>
       <c r="R3" t="n">
-        <v>486393000</v>
+        <v>494878000</v>
       </c>
       <c r="S3" t="n">
         <v>486393000</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.17</v>
+        <v>11.96</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.17</v>
+        <v>12.17</v>
       </c>
       <c r="V3" t="n">
-        <v>-80870000</v>
+        <v>5918495000</v>
       </c>
       <c r="W3" t="n">
-        <v>-80870000</v>
+        <v>5918495000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-80870000</v>
+        <v>5918495000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-235000</v>
+        <v>-77000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-80635000</v>
+        <v>5918572000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-80635000</v>
+        <v>5918572000</v>
       </c>
       <c r="AC3" t="n">
-        <v>203527000</v>
+        <v>292578000</v>
       </c>
       <c r="AD3" t="n">
-        <v>122892000</v>
+        <v>6211150000</v>
       </c>
       <c r="AE3" t="n">
-        <v>132772000</v>
+        <v>6284620000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-304000</v>
+        <v>-6716000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-403000</v>
+        <v>-231000</v>
       </c>
       <c r="AH3" t="n">
-        <v>707000</v>
+        <v>6947000</v>
       </c>
       <c r="AI3" t="n">
-        <v>4629000</v>
+        <v>-19399000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>20977000</v>
+        <v>27012000</v>
       </c>
       <c r="AK3" t="n">
-        <v>25606000</v>
+        <v>7613000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-67753000</v>
+        <v>-385263000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1617393000</v>
+        <v>1831024000</v>
       </c>
       <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="n">
-        <v>18239000</v>
-      </c>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>1599154000</v>
+        <v>1831024000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1180874000</v>
+        <v>1121980000</v>
       </c>
       <c r="AR3" t="n">
-        <v>418280000</v>
+        <v>709044000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1549640000</v>
+        <v>1445761000</v>
       </c>
       <c r="AT3" t="n">
-        <v>9678785000</v>
+        <v>9623679000</v>
       </c>
       <c r="AU3" t="n">
-        <v>11228425000</v>
+        <v>11069440000</v>
       </c>
       <c r="AV3" t="n">
-        <v>11228425000</v>
+        <v>11069440000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-316359.10387</v>
+        <v>-60800</v>
       </c>
       <c r="C4" t="n">
-        <v>0.047105</v>
+        <v>0.2</v>
       </c>
       <c r="D4" t="n">
-        <v>6351666000</v>
+        <v>288333000</v>
       </c>
       <c r="E4" t="n">
-        <v>-6716000</v>
+        <v>-304000</v>
       </c>
       <c r="F4" t="n">
-        <v>-6716000</v>
+        <v>-304000</v>
       </c>
       <c r="G4" t="n">
-        <v>5918495000</v>
+        <v>-80870000</v>
       </c>
       <c r="H4" t="n">
-        <v>106788000</v>
+        <v>144160000</v>
       </c>
       <c r="I4" t="n">
-        <v>9623679000</v>
+        <v>9678785000</v>
       </c>
       <c r="J4" t="n">
-        <v>6344950000</v>
+        <v>288029000</v>
       </c>
       <c r="K4" t="n">
-        <v>6238162000</v>
+        <v>143869000</v>
       </c>
       <c r="L4" t="n">
-        <v>-19399000</v>
+        <v>4629000</v>
       </c>
       <c r="M4" t="n">
-        <v>27012000</v>
+        <v>20977000</v>
       </c>
       <c r="N4" t="n">
-        <v>7613000</v>
+        <v>25606000</v>
       </c>
       <c r="O4" t="n">
-        <v>5924894640.89613</v>
+        <v>-80626800</v>
       </c>
       <c r="P4" t="n">
-        <v>5918495000</v>
+        <v>-80870000</v>
       </c>
       <c r="Q4" t="n">
-        <v>11454703000</v>
+        <v>11296178000</v>
       </c>
       <c r="R4" t="n">
-        <v>494878000</v>
+        <v>486393000</v>
       </c>
       <c r="S4" t="n">
         <v>486393000</v>
       </c>
       <c r="T4" t="n">
-        <v>11.96</v>
+        <v>-0.17</v>
       </c>
       <c r="U4" t="n">
-        <v>12.17</v>
+        <v>-0.17</v>
       </c>
       <c r="V4" t="n">
-        <v>5918495000</v>
+        <v>-80870000</v>
       </c>
       <c r="W4" t="n">
-        <v>5918495000</v>
+        <v>-80870000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>5918495000</v>
+        <v>-80870000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-77000</v>
+        <v>-235000</v>
       </c>
       <c r="AA4" t="n">
-        <v>5918572000</v>
+        <v>-80635000</v>
       </c>
       <c r="AB4" t="n">
-        <v>5918572000</v>
+        <v>-80635000</v>
       </c>
       <c r="AC4" t="n">
-        <v>292578000</v>
+        <v>203527000</v>
       </c>
       <c r="AD4" t="n">
-        <v>6211150000</v>
+        <v>122892000</v>
       </c>
       <c r="AE4" t="n">
-        <v>6284620000</v>
+        <v>132772000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-6716000</v>
+        <v>-304000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-231000</v>
+        <v>-403000</v>
       </c>
       <c r="AH4" t="n">
-        <v>6947000</v>
+        <v>707000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-19399000</v>
+        <v>4629000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>27012000</v>
+        <v>20977000</v>
       </c>
       <c r="AK4" t="n">
-        <v>7613000</v>
+        <v>25606000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-385263000</v>
+        <v>-67753000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1831024000</v>
+        <v>1617393000</v>
       </c>
       <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
+      <c r="AO4" t="n">
+        <v>18239000</v>
+      </c>
       <c r="AP4" t="n">
-        <v>1831024000</v>
+        <v>1599154000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1121980000</v>
+        <v>1180874000</v>
       </c>
       <c r="AR4" t="n">
-        <v>709044000</v>
+        <v>418280000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1445761000</v>
+        <v>1549640000</v>
       </c>
       <c r="AT4" t="n">
-        <v>9623679000</v>
+        <v>9678785000</v>
       </c>
       <c r="AU4" t="n">
-        <v>11069440000</v>
+        <v>11228425000</v>
       </c>
       <c r="AV4" t="n">
-        <v>11069440000</v>
+        <v>11228425000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>32188.430171</v>
+        <v>-1059598.496693</v>
       </c>
       <c r="C5" t="n">
-        <v>0.068632</v>
+        <v>0.157421</v>
       </c>
       <c r="D5" t="n">
-        <v>751295000</v>
+        <v>1040437000</v>
       </c>
       <c r="E5" t="n">
-        <v>469000</v>
+        <v>-6731000</v>
       </c>
       <c r="F5" t="n">
-        <v>469000</v>
+        <v>-6731000</v>
       </c>
       <c r="G5" t="n">
-        <v>591827000</v>
+        <v>742411000</v>
       </c>
       <c r="H5" t="n">
-        <v>104769000</v>
+        <v>148763000</v>
       </c>
       <c r="I5" t="n">
-        <v>8409291000</v>
+        <v>8792097000</v>
       </c>
       <c r="J5" t="n">
-        <v>751764000</v>
+        <v>1033706000</v>
       </c>
       <c r="K5" t="n">
-        <v>646995000</v>
+        <v>884943000</v>
       </c>
       <c r="L5" t="n">
-        <v>-7004000</v>
+        <v>42447000</v>
       </c>
       <c r="M5" t="n">
-        <v>11359000</v>
+        <v>3553000</v>
       </c>
       <c r="N5" t="n">
-        <v>4355000</v>
+        <v>46000000</v>
       </c>
       <c r="O5" t="n">
-        <v>591390188.430171</v>
+        <v>748082401.503307</v>
       </c>
       <c r="P5" t="n">
-        <v>591827000</v>
+        <v>742411000</v>
       </c>
       <c r="Q5" t="n">
-        <v>9735859000</v>
+        <v>10057186000</v>
       </c>
       <c r="R5" t="n">
-        <v>488036000</v>
+        <v>487315000</v>
       </c>
       <c r="S5" t="n">
         <v>486393000</v>
       </c>
       <c r="T5" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="V5" t="n">
-        <v>591827000</v>
+        <v>742411000</v>
       </c>
       <c r="W5" t="n">
-        <v>591827000</v>
+        <v>742411000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>591827000</v>
+        <v>742411000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-184000</v>
+        <v>-230000</v>
       </c>
       <c r="AA5" t="n">
-        <v>592011000</v>
+        <v>742641000</v>
       </c>
       <c r="AB5" t="n">
-        <v>592011000</v>
+        <v>742641000</v>
       </c>
       <c r="AC5" t="n">
-        <v>43625000</v>
+        <v>138749000</v>
       </c>
       <c r="AD5" t="n">
-        <v>635636000</v>
+        <v>881390000</v>
       </c>
       <c r="AE5" t="n">
-        <v>88950000</v>
+        <v>166423000</v>
       </c>
       <c r="AF5" t="n">
-        <v>469000</v>
+        <v>-6731000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-702000</v>
+        <v>-278000</v>
       </c>
       <c r="AH5" t="n">
-        <v>233000</v>
+        <v>7009000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-7004000</v>
+        <v>42447000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11359000</v>
+        <v>3553000</v>
       </c>
       <c r="AK5" t="n">
-        <v>4355000</v>
+        <v>46000000</v>
       </c>
       <c r="AL5" t="n">
-        <v>209119000</v>
+        <v>625259000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1326568000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-471000</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
+        <v>1265089000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="n">
+        <v>29981000</v>
+      </c>
       <c r="AP5" t="n">
-        <v>1326568000</v>
+        <v>1235108000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>955655000</v>
+        <v>960878000</v>
       </c>
       <c r="AR5" t="n">
-        <v>370913000</v>
+        <v>274230000</v>
       </c>
       <c r="AS5" t="n">
-        <v>1535687000</v>
+        <v>1890348000</v>
       </c>
       <c r="AT5" t="n">
-        <v>8409291000</v>
+        <v>8792097000</v>
       </c>
       <c r="AU5" t="n">
-        <v>9944978000</v>
+        <v>10682445000</v>
       </c>
       <c r="AV5" t="n">
-        <v>9944978000</v>
+        <v>10682445000</v>
       </c>
     </row>
   </sheetData>
@@ -1567,7 +1567,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>13679000</v>
@@ -1578,51 +1578,53 @@
       <c r="D2" t="n">
         <v>499999000</v>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>422471000</v>
+      </c>
       <c r="F2" t="n">
-        <v>240114000</v>
+        <v>2090506000</v>
       </c>
       <c r="G2" t="n">
-        <v>12810524000</v>
+        <v>6984113000</v>
       </c>
       <c r="H2" t="n">
-        <v>12829496000</v>
+        <v>9073013000</v>
       </c>
       <c r="I2" t="n">
-        <v>4863631000</v>
+        <v>2219126000</v>
       </c>
       <c r="J2" t="n">
-        <v>12810524000</v>
+        <v>6984113000</v>
       </c>
       <c r="K2" t="n">
-        <v>221142000</v>
+        <v>3475000</v>
       </c>
       <c r="L2" t="n">
-        <v>12810524000</v>
+        <v>6985982000</v>
       </c>
       <c r="M2" t="n">
-        <v>12810524000</v>
+        <v>8035982000</v>
       </c>
       <c r="N2" t="n">
-        <v>12816013000</v>
+        <v>6991127000</v>
       </c>
       <c r="O2" t="n">
-        <v>5489000</v>
+        <v>5145000</v>
       </c>
       <c r="P2" t="n">
-        <v>12810524000</v>
+        <v>6985982000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-112812000</v>
+        <v>-105953000</v>
       </c>
       <c r="R2" t="n">
         <v>203876000</v>
       </c>
       <c r="S2" t="n">
-        <v>6002073000</v>
+        <v>851981000</v>
       </c>
       <c r="T2" t="n">
-        <v>1014497000</v>
+        <v>993134000</v>
       </c>
       <c r="U2" t="n">
         <v>4999990000</v>
@@ -1631,129 +1633,135 @@
         <v>4999990000</v>
       </c>
       <c r="W2" t="n">
-        <v>1828398000</v>
+        <v>3647149000</v>
       </c>
       <c r="X2" t="n">
-        <v>433662000</v>
+        <v>1285231000</v>
       </c>
       <c r="Y2" t="n">
-        <v>7560000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+        <v>6598000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>5119000</v>
+      </c>
       <c r="AA2" t="n">
-        <v>226594000</v>
+        <v>222537000</v>
       </c>
       <c r="AB2" t="n">
-        <v>199508000</v>
+        <v>1050977000</v>
       </c>
       <c r="AC2" t="n">
-        <v>199508000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
+        <v>977000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1050000000</v>
+      </c>
       <c r="AE2" t="n">
-        <v>1394736000</v>
+        <v>2361918000</v>
       </c>
       <c r="AF2" t="n">
-        <v>191636000</v>
+        <v>164163000</v>
       </c>
       <c r="AG2" t="n">
-        <v>40606000</v>
+        <v>1039529000</v>
       </c>
       <c r="AH2" t="n">
-        <v>21634000</v>
+        <v>2498000</v>
       </c>
       <c r="AI2" t="n">
-        <v>18972000</v>
+        <v>1037031000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1157108000</v>
+        <v>1109394000</v>
       </c>
       <c r="AK2" t="n">
-        <v>445888000</v>
+        <v>467193000</v>
       </c>
       <c r="AL2" t="n">
-        <v>99927000</v>
+        <v>64864000</v>
       </c>
       <c r="AM2" t="n">
-        <v>611293000</v>
+        <v>577337000</v>
       </c>
       <c r="AN2" t="n">
-        <v>14644411000</v>
+        <v>10638276000</v>
       </c>
       <c r="AO2" t="n">
-        <v>8386044000</v>
+        <v>6057232000</v>
       </c>
       <c r="AP2" t="n">
-        <v>67902000</v>
+        <v>19850000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3600000000</v>
+        <v>1242000</v>
       </c>
       <c r="AR2" t="n">
-        <v>8743000</v>
+        <v>3059000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1660469000</v>
+        <v>133274000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1660469000</v>
+        <v>133274000</v>
       </c>
       <c r="AU2" t="n">
-        <v>323843000</v>
+        <v>3313918000</v>
       </c>
       <c r="AV2" t="n">
-        <v>609685000</v>
+        <v>614900000</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1869000</v>
       </c>
       <c r="AX2" t="n">
-        <v>2108121000</v>
+        <v>1963036000</v>
       </c>
       <c r="AY2" t="n">
-        <v>2108121000</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
+        <v>1963036000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1242000</v>
+      </c>
       <c r="BA2" t="n">
-        <v>2108121000</v>
+        <v>1961794000</v>
       </c>
       <c r="BB2" t="n">
-        <v>6258367000</v>
+        <v>4581044000</v>
       </c>
       <c r="BC2" t="n">
-        <v>20722000</v>
+        <v>6177000</v>
       </c>
       <c r="BD2" t="n">
-        <v>333503000</v>
+        <v>657721000</v>
       </c>
       <c r="BE2" t="n">
-        <v>1471311000</v>
+        <v>737589000</v>
       </c>
       <c r="BF2" t="n">
-        <v>149118000</v>
+        <v>186261000</v>
       </c>
       <c r="BG2" t="n">
-        <v>3583000</v>
+        <v>1502000</v>
       </c>
       <c r="BH2" t="n">
-        <v>1082467000</v>
+        <v>1221182000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1082467000</v>
+        <v>1221182000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>3197663000</v>
+        <v>1770612000</v>
       </c>
       <c r="BK2" t="n">
-        <v>447544000</v>
+        <v>106052000</v>
       </c>
       <c r="BL2" t="n">
-        <v>2750119000</v>
+        <v>1664560000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>13679000</v>
@@ -1766,49 +1774,49 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>7515000</v>
+        <v>1712433000</v>
       </c>
       <c r="G3" t="n">
-        <v>12078505000</v>
+        <v>12562060000</v>
       </c>
       <c r="H3" t="n">
-        <v>12080728000</v>
+        <v>14272821000</v>
       </c>
       <c r="I3" t="n">
-        <v>4136330000</v>
+        <v>8244152000</v>
       </c>
       <c r="J3" t="n">
-        <v>12078505000</v>
+        <v>12562060000</v>
       </c>
       <c r="K3" t="n">
-        <v>5446000</v>
+        <v>2284000</v>
       </c>
       <c r="L3" t="n">
-        <v>12078659000</v>
+        <v>12562672000</v>
       </c>
       <c r="M3" t="n">
-        <v>12078659000</v>
+        <v>12562672000</v>
       </c>
       <c r="N3" t="n">
-        <v>12084068000</v>
+        <v>12567859000</v>
       </c>
       <c r="O3" t="n">
-        <v>5409000</v>
+        <v>5187000</v>
       </c>
       <c r="P3" t="n">
-        <v>12078659000</v>
+        <v>12562672000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-91700000</v>
+        <v>28205000</v>
       </c>
       <c r="R3" t="n">
         <v>203876000</v>
       </c>
       <c r="S3" t="n">
-        <v>5249096000</v>
+        <v>6213851000</v>
       </c>
       <c r="T3" t="n">
-        <v>1014497000</v>
+        <v>1006742000</v>
       </c>
       <c r="U3" t="n">
         <v>4999990000</v>
@@ -1817,131 +1825,135 @@
         <v>4999990000</v>
       </c>
       <c r="W3" t="n">
-        <v>1595096000</v>
+        <v>4086745000</v>
       </c>
       <c r="X3" t="n">
-        <v>233073000</v>
+        <v>230167000</v>
       </c>
       <c r="Y3" t="n">
-        <v>6630000</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
+        <v>6530000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
       <c r="AA3" t="n">
-        <v>222926000</v>
+        <v>223071000</v>
       </c>
       <c r="AB3" t="n">
-        <v>3517000</v>
+        <v>566000</v>
       </c>
       <c r="AC3" t="n">
-        <v>3517000</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
+        <v>566000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE3" t="n">
-        <v>1362023000</v>
+        <v>3856578000</v>
       </c>
       <c r="AF3" t="n">
-        <v>180670000</v>
+        <v>185800000</v>
       </c>
       <c r="AG3" t="n">
-        <v>3998000</v>
+        <v>1711867000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1929000</v>
+        <v>1718000</v>
       </c>
       <c r="AI3" t="n">
-        <v>2069000</v>
+        <v>1710149000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1171644000</v>
+        <v>1905134000</v>
       </c>
       <c r="AK3" t="n">
-        <v>355324000</v>
+        <v>949854000</v>
       </c>
       <c r="AL3" t="n">
-        <v>254570000</v>
+        <v>339284000</v>
       </c>
       <c r="AM3" t="n">
-        <v>561750000</v>
+        <v>615996000</v>
       </c>
       <c r="AN3" t="n">
-        <v>13679164000</v>
+        <v>16654604000</v>
       </c>
       <c r="AO3" t="n">
-        <v>8180811000</v>
+        <v>4553874000</v>
       </c>
       <c r="AP3" t="n">
-        <v>52239000</v>
+        <v>51783000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3600000000</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>40278000</v>
+        <v>33490000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1585269000</v>
+        <v>1538303000</v>
       </c>
       <c r="AT3" t="n">
-        <v>1585269000</v>
+        <v>1538303000</v>
       </c>
       <c r="AU3" t="n">
-        <v>314127000</v>
+        <v>304201000</v>
       </c>
       <c r="AV3" t="n">
-        <v>611404000</v>
+        <v>613160000</v>
       </c>
       <c r="AW3" t="n">
-        <v>154000</v>
+        <v>612000</v>
       </c>
       <c r="AX3" t="n">
-        <v>1970307000</v>
+        <v>2005260000</v>
       </c>
       <c r="AY3" t="n">
-        <v>1970307000</v>
+        <v>2005260000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>3510000</v>
       </c>
       <c r="BA3" t="n">
-        <v>1970307000</v>
+        <v>2001750000</v>
       </c>
       <c r="BB3" t="n">
-        <v>5498353000</v>
+        <v>12100730000</v>
       </c>
       <c r="BC3" t="n">
-        <v>4417000</v>
+        <v>6348000</v>
       </c>
       <c r="BD3" t="n">
-        <v>663215000</v>
+        <v>404605000</v>
       </c>
       <c r="BE3" t="n">
-        <v>1387770000</v>
+        <v>1591515000</v>
       </c>
       <c r="BF3" t="n">
-        <v>154346000</v>
+        <v>174176000</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>1271474000</v>
+        <v>1318802000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1271474000</v>
+        <v>1318802000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>2017131000</v>
+        <v>8605284000</v>
       </c>
       <c r="BK3" t="n">
-        <v>195549000</v>
+        <v>100872000</v>
       </c>
       <c r="BL3" t="n">
-        <v>1821582000</v>
+        <v>8504412000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>13679000</v>
@@ -1954,49 +1966,49 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>1712433000</v>
+        <v>7515000</v>
       </c>
       <c r="G4" t="n">
-        <v>12562060000</v>
+        <v>12078505000</v>
       </c>
       <c r="H4" t="n">
-        <v>14272821000</v>
+        <v>12080728000</v>
       </c>
       <c r="I4" t="n">
-        <v>8244152000</v>
+        <v>4136330000</v>
       </c>
       <c r="J4" t="n">
-        <v>12562060000</v>
+        <v>12078505000</v>
       </c>
       <c r="K4" t="n">
-        <v>2284000</v>
+        <v>5446000</v>
       </c>
       <c r="L4" t="n">
-        <v>12562672000</v>
+        <v>12078659000</v>
       </c>
       <c r="M4" t="n">
-        <v>12562672000</v>
+        <v>12078659000</v>
       </c>
       <c r="N4" t="n">
-        <v>12567859000</v>
+        <v>12084068000</v>
       </c>
       <c r="O4" t="n">
-        <v>5187000</v>
+        <v>5409000</v>
       </c>
       <c r="P4" t="n">
-        <v>12562672000</v>
+        <v>12078659000</v>
       </c>
       <c r="Q4" t="n">
-        <v>28205000</v>
+        <v>-91700000</v>
       </c>
       <c r="R4" t="n">
         <v>203876000</v>
       </c>
       <c r="S4" t="n">
-        <v>6213851000</v>
+        <v>5249096000</v>
       </c>
       <c r="T4" t="n">
-        <v>1006742000</v>
+        <v>1014497000</v>
       </c>
       <c r="U4" t="n">
         <v>4999990000</v>
@@ -2005,135 +2017,131 @@
         <v>4999990000</v>
       </c>
       <c r="W4" t="n">
-        <v>4086745000</v>
+        <v>1595096000</v>
       </c>
       <c r="X4" t="n">
-        <v>230167000</v>
+        <v>233073000</v>
       </c>
       <c r="Y4" t="n">
-        <v>6530000</v>
-      </c>
-      <c r="Z4" t="n">
+        <v>6630000</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>222926000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>3517000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3517000</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>1362023000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>180670000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3998000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1929000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2069000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1171644000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>355324000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>254570000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>561750000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>13679164000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>8180811000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>52239000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3600000000</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>40278000</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1585269000</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1585269000</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>314127000</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>611404000</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>154000</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1970307000</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1970307000</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>0</v>
       </c>
-      <c r="AA4" t="n">
-        <v>223071000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>566000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>566000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>3856578000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>185800000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1711867000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1718000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1710149000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1905134000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>949854000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>339284000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>615996000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>16654604000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>4553874000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>51783000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>33490000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1538303000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1538303000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>304201000</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>613160000</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>612000</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>2005260000</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>2005260000</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3510000</v>
-      </c>
       <c r="BA4" t="n">
-        <v>2001750000</v>
+        <v>1970307000</v>
       </c>
       <c r="BB4" t="n">
-        <v>12100730000</v>
+        <v>5498353000</v>
       </c>
       <c r="BC4" t="n">
-        <v>6348000</v>
+        <v>4417000</v>
       </c>
       <c r="BD4" t="n">
-        <v>404605000</v>
+        <v>663215000</v>
       </c>
       <c r="BE4" t="n">
-        <v>1591515000</v>
+        <v>1387770000</v>
       </c>
       <c r="BF4" t="n">
-        <v>174176000</v>
+        <v>154346000</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>1318802000</v>
+        <v>1271474000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1318802000</v>
+        <v>1271474000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8605284000</v>
+        <v>2017131000</v>
       </c>
       <c r="BK4" t="n">
-        <v>100872000</v>
+        <v>195549000</v>
       </c>
       <c r="BL4" t="n">
-        <v>8504412000</v>
+        <v>1821582000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>13679000</v>
@@ -2144,53 +2152,51 @@
       <c r="D5" t="n">
         <v>499999000</v>
       </c>
-      <c r="E5" t="n">
-        <v>422471000</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2090506000</v>
+        <v>240114000</v>
       </c>
       <c r="G5" t="n">
-        <v>6984113000</v>
+        <v>12810524000</v>
       </c>
       <c r="H5" t="n">
-        <v>9073013000</v>
+        <v>12829496000</v>
       </c>
       <c r="I5" t="n">
-        <v>2219126000</v>
+        <v>4863631000</v>
       </c>
       <c r="J5" t="n">
-        <v>6984113000</v>
+        <v>12810524000</v>
       </c>
       <c r="K5" t="n">
-        <v>3475000</v>
+        <v>221142000</v>
       </c>
       <c r="L5" t="n">
-        <v>6985982000</v>
+        <v>12810524000</v>
       </c>
       <c r="M5" t="n">
-        <v>8035982000</v>
+        <v>12810524000</v>
       </c>
       <c r="N5" t="n">
-        <v>6991127000</v>
+        <v>12816013000</v>
       </c>
       <c r="O5" t="n">
-        <v>5145000</v>
+        <v>5489000</v>
       </c>
       <c r="P5" t="n">
-        <v>6985982000</v>
+        <v>12810524000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-105953000</v>
+        <v>-112812000</v>
       </c>
       <c r="R5" t="n">
         <v>203876000</v>
       </c>
       <c r="S5" t="n">
-        <v>851981000</v>
+        <v>6002073000</v>
       </c>
       <c r="T5" t="n">
-        <v>993134000</v>
+        <v>1014497000</v>
       </c>
       <c r="U5" t="n">
         <v>4999990000</v>
@@ -2199,130 +2205,124 @@
         <v>4999990000</v>
       </c>
       <c r="W5" t="n">
-        <v>3647149000</v>
+        <v>1828398000</v>
       </c>
       <c r="X5" t="n">
-        <v>1285231000</v>
+        <v>433662000</v>
       </c>
       <c r="Y5" t="n">
-        <v>6598000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5119000</v>
-      </c>
+        <v>7560000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>222537000</v>
+        <v>226594000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1050977000</v>
+        <v>199508000</v>
       </c>
       <c r="AC5" t="n">
-        <v>977000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1050000000</v>
-      </c>
+        <v>199508000</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>2361918000</v>
+        <v>1394736000</v>
       </c>
       <c r="AF5" t="n">
-        <v>164163000</v>
+        <v>191636000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1039529000</v>
+        <v>40606000</v>
       </c>
       <c r="AH5" t="n">
-        <v>2498000</v>
+        <v>21634000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1037031000</v>
+        <v>18972000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1109394000</v>
+        <v>1157108000</v>
       </c>
       <c r="AK5" t="n">
-        <v>467193000</v>
+        <v>445888000</v>
       </c>
       <c r="AL5" t="n">
-        <v>64864000</v>
+        <v>99927000</v>
       </c>
       <c r="AM5" t="n">
-        <v>577337000</v>
+        <v>611293000</v>
       </c>
       <c r="AN5" t="n">
-        <v>10638276000</v>
+        <v>14644411000</v>
       </c>
       <c r="AO5" t="n">
-        <v>6057232000</v>
+        <v>8386044000</v>
       </c>
       <c r="AP5" t="n">
-        <v>19850000</v>
+        <v>67902000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1242000</v>
+        <v>3600000000</v>
       </c>
       <c r="AR5" t="n">
-        <v>3059000</v>
+        <v>8743000</v>
       </c>
       <c r="AS5" t="n">
-        <v>133274000</v>
+        <v>1660469000</v>
       </c>
       <c r="AT5" t="n">
-        <v>133274000</v>
+        <v>1660469000</v>
       </c>
       <c r="AU5" t="n">
-        <v>3313918000</v>
+        <v>323843000</v>
       </c>
       <c r="AV5" t="n">
-        <v>614900000</v>
+        <v>609685000</v>
       </c>
       <c r="AW5" t="n">
-        <v>1869000</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1963036000</v>
+        <v>2108121000</v>
       </c>
       <c r="AY5" t="n">
-        <v>1963036000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1242000</v>
-      </c>
+        <v>2108121000</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>1961794000</v>
+        <v>2108121000</v>
       </c>
       <c r="BB5" t="n">
-        <v>4581044000</v>
+        <v>6258367000</v>
       </c>
       <c r="BC5" t="n">
-        <v>6177000</v>
+        <v>20722000</v>
       </c>
       <c r="BD5" t="n">
-        <v>657721000</v>
+        <v>333503000</v>
       </c>
       <c r="BE5" t="n">
-        <v>737589000</v>
+        <v>1471311000</v>
       </c>
       <c r="BF5" t="n">
-        <v>186261000</v>
+        <v>149118000</v>
       </c>
       <c r="BG5" t="n">
-        <v>1502000</v>
+        <v>3583000</v>
       </c>
       <c r="BH5" t="n">
-        <v>1221182000</v>
+        <v>1082467000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1221182000</v>
+        <v>1082467000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1770612000</v>
+        <v>3197663000</v>
       </c>
       <c r="BK5" t="n">
-        <v>106052000</v>
+        <v>447544000</v>
       </c>
       <c r="BL5" t="n">
-        <v>1664560000</v>
+        <v>2750119000</v>
       </c>
     </row>
   </sheetData>
@@ -2593,598 +2593,598 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1151999000</v>
+        <v>-522570000</v>
       </c>
       <c r="C2" t="n">
-        <v>-4422658000</v>
+        <v>-9161776000</v>
       </c>
       <c r="D2" t="n">
-        <v>4440658000</v>
+        <v>10480061000</v>
       </c>
       <c r="E2" t="n">
-        <v>-65486000</v>
+        <v>-249019000</v>
       </c>
       <c r="F2" t="n">
-        <v>2750119000</v>
+        <v>1664560000</v>
       </c>
       <c r="G2" t="n">
-        <v>1821582000</v>
+        <v>772454000</v>
       </c>
       <c r="H2" t="n">
-        <v>12753000</v>
+        <v>-624000</v>
       </c>
       <c r="I2" t="n">
-        <v>915784000</v>
+        <v>892730000</v>
       </c>
       <c r="J2" t="n">
-        <v>12985000</v>
+        <v>635929000</v>
       </c>
       <c r="K2" t="n">
-        <v>930000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>1299000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-680948000</v>
+      </c>
       <c r="M2" t="n">
-        <v>18000000</v>
+        <v>1318285000</v>
       </c>
       <c r="N2" t="n">
-        <v>18000000</v>
+        <v>868285000</v>
       </c>
       <c r="O2" t="n">
-        <v>-4422658000</v>
+        <v>-9161776000</v>
       </c>
       <c r="P2" t="n">
-        <v>4440658000</v>
+        <v>10030061000</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>450000000</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>450000000</v>
+      </c>
       <c r="T2" t="n">
-        <v>-314686000</v>
+        <v>530352000</v>
       </c>
       <c r="U2" t="n">
-        <v>90980000</v>
+        <v>419834000</v>
       </c>
       <c r="V2" t="n">
-        <v>-347063000</v>
+        <v>355146000</v>
       </c>
       <c r="W2" t="n">
-        <v>500819000</v>
+        <v>370032000</v>
       </c>
       <c r="X2" t="n">
-        <v>-847882000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
+        <v>-14886000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
       <c r="AC2" t="n">
-        <v>-58603000</v>
+        <v>-244628000</v>
       </c>
       <c r="AD2" t="n">
-        <v>6883000</v>
+        <v>4391000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-65486000</v>
+        <v>-249019000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1217485000</v>
+        <v>-273551000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-264880000</v>
+        <v>-5266000</v>
       </c>
       <c r="AH2" t="n">
-        <v>39630000</v>
+        <v>4355000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1292000</v>
+        <v>-11359000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>567656000</v>
+        <v>-644042000</v>
       </c>
       <c r="AK2" t="n">
-        <v>9869000</v>
+        <v>25574000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-44150000</v>
+        <v>-18053000</v>
       </c>
       <c r="AM2" t="n">
-        <v>140107000</v>
+        <v>51709000</v>
       </c>
       <c r="AN2" t="n">
-        <v>352276000</v>
+        <v>-338071000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-82076000</v>
+        <v>-139166000</v>
       </c>
       <c r="AP2" t="n">
-        <v>193596000</v>
+        <v>-225047000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-41913000</v>
+        <v>7235000</v>
       </c>
       <c r="AR2" t="n">
-        <v>7009000</v>
+        <v>233000</v>
       </c>
       <c r="AS2" t="n">
-        <v>148763000</v>
+        <v>104769000</v>
       </c>
       <c r="AT2" t="n">
-        <v>154000</v>
+        <v>2542000</v>
       </c>
       <c r="AU2" t="n">
-        <v>148609000</v>
+        <v>102227000</v>
       </c>
       <c r="AV2" t="n">
-        <v>-64194000</v>
+        <v>-20356000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-692000</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+        <v>-654000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
       <c r="AY2" t="n">
-        <v>881390000</v>
+        <v>635636000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-1038176000</v>
+        <v>-576797000</v>
       </c>
       <c r="C3" t="n">
-        <v>-5003458000</v>
+        <v>-13310038000</v>
       </c>
       <c r="D3" t="n">
-        <v>3293968000</v>
+        <v>12933216000</v>
       </c>
       <c r="E3" t="n">
-        <v>-108252000</v>
+        <v>-145896000</v>
       </c>
       <c r="F3" t="n">
-        <v>1821582000</v>
+        <v>8504412000</v>
       </c>
       <c r="G3" t="n">
-        <v>8504412000</v>
+        <v>1664560000</v>
       </c>
       <c r="H3" t="n">
-        <v>6604000</v>
+        <v>4983000</v>
       </c>
       <c r="I3" t="n">
-        <v>-6689434000</v>
+        <v>6834869000</v>
       </c>
       <c r="J3" t="n">
-        <v>-1997515000</v>
+        <v>-866030000</v>
       </c>
       <c r="K3" t="n">
-        <v>100000</v>
+        <v>-90000</v>
       </c>
       <c r="L3" t="n">
-        <v>-284928000</v>
+        <v>-486391000</v>
       </c>
       <c r="M3" t="n">
-        <v>-1709490000</v>
+        <v>-376822000</v>
       </c>
       <c r="N3" t="n">
-        <v>-1139490000</v>
+        <v>103178000</v>
       </c>
       <c r="O3" t="n">
-        <v>-4433458000</v>
+        <v>-12830038000</v>
       </c>
       <c r="P3" t="n">
-        <v>3293968000</v>
+        <v>12933216000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-570000000</v>
+        <v>-480000000</v>
       </c>
       <c r="R3" t="n">
-        <v>-570000000</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
+        <v>-480000000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
       <c r="T3" t="n">
-        <v>-3761995000</v>
+        <v>8131800000</v>
       </c>
       <c r="U3" t="n">
-        <v>95129000</v>
+        <v>280641000</v>
       </c>
       <c r="V3" t="n">
-        <v>-3757345000</v>
+        <v>3834000</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>379286000</v>
       </c>
       <c r="X3" t="n">
-        <v>-3757345000</v>
+        <v>3834000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>7986979000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>7986979000</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>-99779000</v>
+        <v>-139654000</v>
       </c>
       <c r="AD3" t="n">
-        <v>8473000</v>
+        <v>6242000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-108252000</v>
+        <v>-145896000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-929924000</v>
+        <v>-430901000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-295174000</v>
+        <v>-44628000</v>
       </c>
       <c r="AH3" t="n">
-        <v>25606000</v>
+        <v>7613000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-20894000</v>
+        <v>-27012000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-780541000</v>
+        <v>-160334000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-7920000</v>
+        <v>21212000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-136012000</v>
+        <v>7328000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-648776000</v>
+        <v>524845000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-260947000</v>
+        <v>253163000</v>
       </c>
       <c r="AO3" t="n">
-        <v>207119000</v>
+        <v>-858229000</v>
       </c>
       <c r="AP3" t="n">
-        <v>66451000</v>
+        <v>-104383000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-10120000</v>
+        <v>19798000</v>
       </c>
       <c r="AR3" t="n">
-        <v>707000</v>
+        <v>6947000</v>
       </c>
       <c r="AS3" t="n">
-        <v>144160000</v>
+        <v>106788000</v>
       </c>
       <c r="AT3" t="n">
-        <v>458000</v>
+        <v>1257000</v>
       </c>
       <c r="AU3" t="n">
-        <v>143702000</v>
+        <v>105531000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-60215000</v>
+        <v>-1595000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-2680000</v>
+        <v>-648000</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>-6211072000</v>
       </c>
       <c r="AY3" t="n">
-        <v>122892000</v>
+        <v>6211150000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-576797000</v>
+        <v>-1038176000</v>
       </c>
       <c r="C4" t="n">
-        <v>-13310038000</v>
+        <v>-5003458000</v>
       </c>
       <c r="D4" t="n">
-        <v>12933216000</v>
+        <v>3293968000</v>
       </c>
       <c r="E4" t="n">
-        <v>-145896000</v>
+        <v>-108252000</v>
       </c>
       <c r="F4" t="n">
+        <v>1821582000</v>
+      </c>
+      <c r="G4" t="n">
         <v>8504412000</v>
       </c>
-      <c r="G4" t="n">
-        <v>1664560000</v>
-      </c>
       <c r="H4" t="n">
-        <v>4983000</v>
+        <v>6604000</v>
       </c>
       <c r="I4" t="n">
-        <v>6834869000</v>
+        <v>-6689434000</v>
       </c>
       <c r="J4" t="n">
-        <v>-866030000</v>
+        <v>-1997515000</v>
       </c>
       <c r="K4" t="n">
-        <v>-90000</v>
+        <v>100000</v>
       </c>
       <c r="L4" t="n">
-        <v>-486391000</v>
+        <v>-284928000</v>
       </c>
       <c r="M4" t="n">
-        <v>-376822000</v>
+        <v>-1709490000</v>
       </c>
       <c r="N4" t="n">
-        <v>103178000</v>
+        <v>-1139490000</v>
       </c>
       <c r="O4" t="n">
-        <v>-12830038000</v>
+        <v>-4433458000</v>
       </c>
       <c r="P4" t="n">
-        <v>12933216000</v>
+        <v>3293968000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-480000000</v>
+        <v>-570000000</v>
       </c>
       <c r="R4" t="n">
-        <v>-480000000</v>
-      </c>
-      <c r="S4" t="n">
+        <v>-570000000</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>-3761995000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>95129000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-3757345000</v>
+      </c>
+      <c r="W4" t="n">
         <v>0</v>
       </c>
-      <c r="T4" t="n">
-        <v>8131800000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>280641000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>3834000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>379286000</v>
-      </c>
       <c r="X4" t="n">
-        <v>3834000</v>
+        <v>-3757345000</v>
       </c>
       <c r="Y4" t="n">
-        <v>7986979000</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>7986979000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>-139654000</v>
+        <v>-99779000</v>
       </c>
       <c r="AD4" t="n">
-        <v>6242000</v>
+        <v>8473000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-145896000</v>
+        <v>-108252000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-430901000</v>
+        <v>-929924000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-44628000</v>
+        <v>-295174000</v>
       </c>
       <c r="AH4" t="n">
-        <v>7613000</v>
+        <v>25606000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-27012000</v>
+        <v>-20894000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-160334000</v>
+        <v>-780541000</v>
       </c>
       <c r="AK4" t="n">
-        <v>21212000</v>
+        <v>-7920000</v>
       </c>
       <c r="AL4" t="n">
-        <v>7328000</v>
+        <v>-136012000</v>
       </c>
       <c r="AM4" t="n">
-        <v>524845000</v>
+        <v>-648776000</v>
       </c>
       <c r="AN4" t="n">
-        <v>253163000</v>
+        <v>-260947000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-858229000</v>
+        <v>207119000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-104383000</v>
+        <v>66451000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19798000</v>
+        <v>-10120000</v>
       </c>
       <c r="AR4" t="n">
-        <v>6947000</v>
+        <v>707000</v>
       </c>
       <c r="AS4" t="n">
-        <v>106788000</v>
+        <v>144160000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1257000</v>
+        <v>458000</v>
       </c>
       <c r="AU4" t="n">
-        <v>105531000</v>
+        <v>143702000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-1595000</v>
+        <v>-60215000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-648000</v>
+        <v>-2680000</v>
       </c>
       <c r="AX4" t="n">
-        <v>-6211072000</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>6211150000</v>
+        <v>122892000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-522570000</v>
+        <v>1151999000</v>
       </c>
       <c r="C5" t="n">
-        <v>-9161776000</v>
+        <v>-4422658000</v>
       </c>
       <c r="D5" t="n">
-        <v>10480061000</v>
+        <v>4440658000</v>
       </c>
       <c r="E5" t="n">
-        <v>-249019000</v>
+        <v>-65486000</v>
       </c>
       <c r="F5" t="n">
-        <v>1664560000</v>
+        <v>2750119000</v>
       </c>
       <c r="G5" t="n">
-        <v>772454000</v>
+        <v>1821582000</v>
       </c>
       <c r="H5" t="n">
-        <v>-624000</v>
+        <v>12753000</v>
       </c>
       <c r="I5" t="n">
-        <v>892730000</v>
+        <v>915784000</v>
       </c>
       <c r="J5" t="n">
-        <v>635929000</v>
+        <v>12985000</v>
       </c>
       <c r="K5" t="n">
-        <v>1299000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-680948000</v>
-      </c>
+        <v>930000</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>1318285000</v>
+        <v>18000000</v>
       </c>
       <c r="N5" t="n">
-        <v>868285000</v>
+        <v>18000000</v>
       </c>
       <c r="O5" t="n">
-        <v>-9161776000</v>
+        <v>-4422658000</v>
       </c>
       <c r="P5" t="n">
-        <v>10030061000</v>
+        <v>4440658000</v>
       </c>
       <c r="Q5" t="n">
-        <v>450000000</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="n">
-        <v>450000000</v>
-      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>530352000</v>
+        <v>-314686000</v>
       </c>
       <c r="U5" t="n">
-        <v>419834000</v>
+        <v>90980000</v>
       </c>
       <c r="V5" t="n">
-        <v>355146000</v>
+        <v>-347063000</v>
       </c>
       <c r="W5" t="n">
-        <v>370032000</v>
+        <v>500819000</v>
       </c>
       <c r="X5" t="n">
-        <v>-14886000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
+        <v>-847882000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>-244628000</v>
+        <v>-58603000</v>
       </c>
       <c r="AD5" t="n">
-        <v>4391000</v>
+        <v>6883000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-249019000</v>
+        <v>-65486000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-273551000</v>
+        <v>1217485000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-5266000</v>
+        <v>-264880000</v>
       </c>
       <c r="AH5" t="n">
-        <v>4355000</v>
+        <v>39630000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-11359000</v>
+        <v>-1292000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-644042000</v>
+        <v>567656000</v>
       </c>
       <c r="AK5" t="n">
-        <v>25574000</v>
+        <v>9869000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-18053000</v>
+        <v>-44150000</v>
       </c>
       <c r="AM5" t="n">
-        <v>51709000</v>
+        <v>140107000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-338071000</v>
+        <v>352276000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-139166000</v>
+        <v>-82076000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-225047000</v>
+        <v>193596000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7235000</v>
+        <v>-41913000</v>
       </c>
       <c r="AR5" t="n">
-        <v>233000</v>
+        <v>7009000</v>
       </c>
       <c r="AS5" t="n">
-        <v>104769000</v>
+        <v>148763000</v>
       </c>
       <c r="AT5" t="n">
-        <v>2542000</v>
+        <v>154000</v>
       </c>
       <c r="AU5" t="n">
-        <v>102227000</v>
+        <v>148609000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-20356000</v>
+        <v>-64194000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-654000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
+        <v>-692000</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>635636000</v>
+        <v>881390000</v>
       </c>
     </row>
   </sheetData>
@@ -3198,7 +3198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EN2"/>
+  <dimension ref="A1:EO2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3354,570 +3354,575 @@
       </c>
       <c r="AE1" t="inlineStr">
         <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
           <t>trailingPE</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>forwardPE</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>regularMarketVolume</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>averageVolume</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>averageVolume10days</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>averageDailyVolume10Day</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ask</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>bidSize</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>askSize</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>marketCap</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>nonDilutedMarketCap</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLow</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>allTimeHigh</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>allTimeLow</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>fiftyDayAverage</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>twoHundredDayAverage</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendRate</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendYield</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>tradeable</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>enterpriseValue</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>profitMargins</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>floatShares</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>sharesOutstanding</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>heldPercentInsiders</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>heldPercentInstitutions</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>impliedSharesOutstanding</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>bookValue</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>lastFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>nextFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>mostRecentQuarter</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>earningsQuarterlyGrowth</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>netIncomeToCommon</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>trailingEps</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>forwardEps</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>lastSplitFactor</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>lastSplitDate</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>enterpriseToRevenue</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>enterpriseToEbitda</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>52WeekChange</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>SandP52WeekChange</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>lastDividendValue</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>lastDividendDate</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>quoteType</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>currentPrice</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>earningsGrowth</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4009,366 +4014,366 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>19.3</v>
+        <v>17.9</v>
       </c>
       <c r="T2" t="n">
-        <v>19.3</v>
+        <v>17.9</v>
       </c>
       <c r="U2" t="n">
-        <v>19.15</v>
+        <v>17.8</v>
       </c>
       <c r="V2" t="n">
-        <v>19.5</v>
+        <v>17.95</v>
       </c>
       <c r="W2" t="n">
-        <v>19.3</v>
+        <v>17.9</v>
       </c>
       <c r="X2" t="n">
-        <v>19.3</v>
+        <v>17.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.15</v>
+        <v>17.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.5</v>
+        <v>17.95</v>
       </c>
       <c r="AA2" t="n">
         <v>1.32</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.8</v>
+        <v>7.42</v>
       </c>
       <c r="AC2" t="n">
         <v>1781222400</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.0385</v>
+        <v>0.84910005</v>
       </c>
       <c r="AE2" t="n">
-        <v>14.923078</v>
+        <v>0.151</v>
       </c>
       <c r="AF2" t="n">
-        <v>15.901639</v>
+        <v>11.194968</v>
       </c>
       <c r="AG2" t="n">
-        <v>1329533</v>
+        <v>14.590163</v>
       </c>
       <c r="AH2" t="n">
-        <v>1329533</v>
+        <v>894912</v>
       </c>
       <c r="AI2" t="n">
-        <v>881784</v>
+        <v>894912</v>
       </c>
       <c r="AJ2" t="n">
-        <v>770686</v>
+        <v>934006</v>
       </c>
       <c r="AK2" t="n">
-        <v>770686</v>
+        <v>1697812</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1697812</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>17.9</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>9434607616</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9385976000</v>
+        <v>8656495616</v>
       </c>
       <c r="AR2" t="n">
+        <v>8705128000</v>
+      </c>
+      <c r="AS2" t="n">
         <v>17.75</v>
       </c>
-      <c r="AS2" t="n">
-        <v>22.5</v>
-      </c>
       <c r="AT2" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="AU2" t="n">
         <v>47.95</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AV2" t="n">
         <v>1.809199</v>
       </c>
-      <c r="AV2" t="n">
-        <v>0.9186838000000001</v>
-      </c>
       <c r="AW2" t="n">
-        <v>18.981</v>
+        <v>0.84291613</v>
       </c>
       <c r="AX2" t="n">
-        <v>18.6095</v>
+        <v>18.867</v>
       </c>
       <c r="AY2" t="n">
+        <v>18.6165</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>1.32</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>0.06839379</v>
-      </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BA2" t="n">
+        <v>0.07374302000000001</v>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>TWD</t>
         </is>
       </c>
-      <c r="BB2" t="b">
+      <c r="BC2" t="b">
         <v>0</v>
       </c>
-      <c r="BC2" t="n">
-        <v>8157547008</v>
-      </c>
       <c r="BD2" t="n">
+        <v>7342403072</v>
+      </c>
+      <c r="BE2" t="n">
         <v>0.07289</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BF2" t="n">
         <v>202372342</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BG2" t="n">
         <v>486320000</v>
       </c>
-      <c r="BG2" t="n">
+      <c r="BH2" t="n">
         <v>0.55966</v>
       </c>
-      <c r="BH2" t="n">
-        <v>0.03076</v>
-      </c>
       <c r="BI2" t="n">
+        <v>0.03092</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>486320000</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BK2" t="n">
         <v>25.662</v>
       </c>
-      <c r="BK2" t="n">
-        <v>0.7559815600000001</v>
-      </c>
       <c r="BL2" t="n">
+        <v>0.69363254</v>
+      </c>
+      <c r="BM2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BM2" t="n">
+      <c r="BN2" t="n">
         <v>1798675200</v>
       </c>
-      <c r="BN2" t="n">
+      <c r="BO2" t="n">
         <v>1774915200</v>
       </c>
-      <c r="BO2" t="n">
+      <c r="BP2" t="n">
         <v>-0.134</v>
       </c>
-      <c r="BP2" t="n">
+      <c r="BQ2" t="n">
         <v>748539008</v>
       </c>
-      <c r="BQ2" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BR2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BS2" t="n">
         <v>1.22</v>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>1.03:1</t>
         </is>
       </c>
-      <c r="BT2" t="n">
+      <c r="BU2" t="n">
         <v>1345075200</v>
       </c>
-      <c r="BU2" t="n">
-        <v>0.794</v>
-      </c>
       <c r="BV2" t="n">
-        <v>13.476</v>
+        <v>0.715</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0.07655501000000001</v>
+        <v>12.115</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.27294624</v>
+        <v>-0.18264842</v>
       </c>
       <c r="BY2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="BZ2" t="n">
         <v>1.32</v>
       </c>
-      <c r="BZ2" t="n">
+      <c r="CA2" t="n">
         <v>1781222400</v>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="CB2" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CC2" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="CD2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="CD2" t="n">
-        <v>1442779008</v>
-      </c>
       <c r="CE2" t="n">
-        <v>2.967</v>
+        <v>1479810944</v>
       </c>
       <c r="CF2" t="n">
-        <v>605336000</v>
+        <v>3.043</v>
       </c>
       <c r="CG2" t="n">
+        <v>606057984</v>
+      </c>
+      <c r="CH2" t="n">
         <v>156434000</v>
       </c>
-      <c r="CH2" t="n">
-        <v>1.525</v>
-      </c>
       <c r="CI2" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="CJ2" t="n">
         <v>2.708</v>
       </c>
-      <c r="CJ2" t="n">
+      <c r="CK2" t="n">
         <v>10269700096</v>
       </c>
-      <c r="CK2" t="n">
+      <c r="CL2" t="n">
         <v>1.253</v>
       </c>
-      <c r="CL2" t="n">
-        <v>21.117</v>
-      </c>
       <c r="CM2" t="n">
+        <v>21.114</v>
+      </c>
+      <c r="CN2" t="n">
         <v>0.02001</v>
       </c>
-      <c r="CN2" t="n">
+      <c r="CO2" t="n">
         <v>0.06052</v>
       </c>
-      <c r="CO2" t="n">
+      <c r="CP2" t="n">
         <v>1814787968</v>
       </c>
-      <c r="CP2" t="n">
-        <v>-77696872</v>
-      </c>
       <c r="CQ2" t="n">
+        <v>-40664876</v>
+      </c>
+      <c r="CR2" t="n">
         <v>199580000</v>
       </c>
-      <c r="CR2" t="n">
-        <v>-0.125</v>
-      </c>
       <c r="CS2" t="n">
+        <v>-0.135</v>
+      </c>
+      <c r="CT2" t="n">
         <v>0.062</v>
       </c>
-      <c r="CT2" t="n">
+      <c r="CU2" t="n">
         <v>0.17671</v>
       </c>
-      <c r="CU2" t="n">
-        <v>0.05894</v>
-      </c>
       <c r="CV2" t="n">
+        <v>0.05901</v>
+      </c>
+      <c r="CW2" t="n">
         <v>0.06311</v>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
         <is>
           <t>TWD</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
         <is>
           <t>1218.TW</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DA2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DB2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DC2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DC2" t="b">
+      <c r="DD2" t="b">
         <v>0</v>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>[{'header': 'Dividend', 'message': '1218.TW announced a cash dividend of TWD 1.32 with an ex-date of Jun. 12, 2026', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1781193600000, 'amount': '1.32'}}]</t>
-        </is>
-      </c>
-      <c r="DF2" t="n">
-        <v>1780378201</v>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>Taisun Enterprise Co., Ltd.</t>
+        </is>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>1782106239</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>TAISUN ENTERPRISE CO. LTD.</t>
+        </is>
+      </c>
+      <c r="DK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="inlineStr">
         <is>
           <t>TAI</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>finmb_12721400</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>Asia/Taipei</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DO2" t="inlineStr">
         <is>
           <t>CST</t>
         </is>
       </c>
-      <c r="DL2" t="n">
+      <c r="DP2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>tw_market</t>
         </is>
       </c>
-      <c r="DN2" t="b">
+      <c r="DR2" t="b">
         <v>0</v>
       </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>Taisun Enterprise Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="DP2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.5181367</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>19.4</v>
-      </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>TAISUN ENTERPRISE CO. LTD.</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="DT2" t="n">
-        <v>0.10000038</v>
+        <v>-0.10000038</v>
       </c>
       <c r="DU2" t="inlineStr">
         <is>
-          <t>19.15 - 19.5</t>
+          <t>17.8 - 17.95</t>
         </is>
       </c>
       <c r="DV2" t="inlineStr">
@@ -4377,45 +4382,45 @@
         </is>
       </c>
       <c r="DW2" t="n">
-        <v>881784</v>
+        <v>934006</v>
       </c>
       <c r="DX2" t="n">
-        <v>1.6499996</v>
+        <v>0.049999237</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.09295773</v>
+        <v>0.0028168585</v>
       </c>
       <c r="DZ2" t="inlineStr">
         <is>
-          <t>17.75 - 22.5</t>
+          <t>17.75 - 22.05</t>
         </is>
       </c>
       <c r="EA2" t="n">
-        <v>-3.1000004</v>
+        <v>-4.25</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0.13777779</v>
+        <v>-0.19274378</v>
       </c>
       <c r="EC2" t="n">
-        <v>-7.6555014</v>
+        <v>-18.264843</v>
       </c>
       <c r="ED2" t="n">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="EE2" t="n">
         <v>1.22</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.41899872</v>
+        <v>-1.0670013</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.022074638</v>
+        <v>-0.05655384</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.79049873</v>
+        <v>-0.8165016</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.042478234</v>
+        <v>-0.043859027</v>
       </c>
       <c r="EJ2" t="n">
         <v>20</v>
@@ -4429,7 +4434,10 @@
       <c r="EM2" t="n">
         <v>946947600000</v>
       </c>
-      <c r="EN2" t="inlineStr"/>
+      <c r="EN2" t="n">
+        <v>-0.55866134</v>
+      </c>
+      <c r="EO2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
